--- a/KUT_DOCS_WORKING/issued/KUT_Master_Information_Delivery_Plan.xlsx
+++ b/KUT_DOCS_WORKING/issued/KUT_Master_Information_Delivery_Plan.xlsx
@@ -682,7 +682,7 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>A1 — Authorised for use</t>
+          <t>DRAFT — not issued (S0, work in progress)</t>
         </is>
       </c>
     </row>
@@ -851,7 +851,7 @@
     <row r="32">
       <c r="B32" s="10" t="inlineStr">
         <is>
-          <t>Issued through the Common Data Environment. Uncontrolled when printed.</t>
+          <t>Not yet issued through the Common Data Environment. Uncontrolled when printed.</t>
         </is>
       </c>
     </row>

--- a/KUT_DOCS_WORKING/issued/KUT_Master_Information_Delivery_Plan.xlsx
+++ b/KUT_DOCS_WORKING/issued/KUT_Master_Information_Delivery_Plan.xlsx
@@ -658,7 +658,7 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>KUT-SMB-ZZ-ZZ-SC-Z-0001</t>
+          <t>KUT-SMB-ZZ-ZZ-SH-Z-0001</t>
         </is>
       </c>
     </row>

--- a/KUT_DOCS_WORKING/issued/KUT_Master_Information_Delivery_Plan.xlsx
+++ b/KUT_DOCS_WORKING/issued/KUT_Master_Information_Delivery_Plan.xlsx
@@ -658,7 +658,7 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>KUT-SMB-ZZ-ZZ-SC-Z-0001</t>
+          <t>KUT-SMB-ZZ-ZZ-SH-Z-0001</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>A1 — Authorised for use</t>
+          <t>DRAFT — not issued (S0, work in progress)</t>
         </is>
       </c>
     </row>
@@ -851,7 +851,7 @@
     <row r="32">
       <c r="B32" s="10" t="inlineStr">
         <is>
-          <t>Issued through the Common Data Environment. Uncontrolled when printed.</t>
+          <t>Not yet issued through the Common Data Environment. Uncontrolled when printed.</t>
         </is>
       </c>
     </row>

--- a/KUT_DOCS_WORKING/issued/KUT_Master_Information_Delivery_Plan.xlsx
+++ b/KUT_DOCS_WORKING/issued/KUT_Master_Information_Delivery_Plan.xlsx
@@ -861,6 +861,14 @@
     <mergeCell ref="B7:C7"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter>
+    <oddHeader>&amp;RDRAFT</oddHeader>
+    <oddFooter>&amp;LDRAFT - not issued (S0, work in progress)&amp;RPage &amp;P of &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1960,6 +1968,14 @@
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader>&amp;RDRAFT</oddHeader>
+    <oddFooter>&amp;LDRAFT - not issued (S0, work in progress)&amp;RPage &amp;P of &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -3051,6 +3067,14 @@
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader>&amp;RDRAFT</oddHeader>
+    <oddFooter>&amp;LDRAFT - not issued (S0, work in progress)&amp;RPage &amp;P of &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -4334,6 +4358,14 @@
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader>&amp;RDRAFT</oddHeader>
+    <oddFooter>&amp;LDRAFT - not issued (S0, work in progress)&amp;RPage &amp;P of &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -5233,6 +5265,14 @@
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader>&amp;RDRAFT</oddHeader>
+    <oddFooter>&amp;LDRAFT - not issued (S0, work in progress)&amp;RPage &amp;P of &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -6332,6 +6372,14 @@
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader>&amp;RDRAFT</oddHeader>
+    <oddFooter>&amp;LDRAFT - not issued (S0, work in progress)&amp;RPage &amp;P of &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -7431,6 +7479,14 @@
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader>&amp;RDRAFT</oddHeader>
+    <oddFooter>&amp;LDRAFT - not issued (S0, work in progress)&amp;RPage &amp;P of &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -8428,6 +8484,14 @@
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader>&amp;RDRAFT</oddHeader>
+    <oddFooter>&amp;LDRAFT - not issued (S0, work in progress)&amp;RPage &amp;P of &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -9692,6 +9756,14 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader>&amp;RDRAFT</oddHeader>
+    <oddFooter>&amp;LDRAFT - not issued (S0, work in progress)&amp;RPage &amp;P of &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -10876,6 +10948,14 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader>&amp;RDRAFT</oddHeader>
+    <oddFooter>&amp;LDRAFT - not issued (S0, work in progress)&amp;RPage &amp;P of &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -12906,6 +12986,14 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader>&amp;RDRAFT</oddHeader>
+    <oddFooter>&amp;LDRAFT - not issued (S0, work in progress)&amp;RPage &amp;P of &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -13240,6 +13328,14 @@
     <mergeCell ref="B20:G21"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter>
+    <oddHeader>&amp;RDRAFT</oddHeader>
+    <oddFooter>&amp;LDRAFT - not issued (S0, work in progress)&amp;RPage &amp;P of &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -13989,6 +14085,14 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter>
+    <oddHeader>&amp;RDRAFT</oddHeader>
+    <oddFooter>&amp;LDRAFT - not issued (S0, work in progress)&amp;RPage &amp;P of &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -26669,6 +26773,14 @@
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader>&amp;RDRAFT</oddHeader>
+    <oddFooter>&amp;LDRAFT - not issued (S0, work in progress)&amp;RPage &amp;P of &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -32436,6 +32548,14 @@
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader>&amp;RDRAFT</oddHeader>
+    <oddFooter>&amp;LDRAFT - not issued (S0, work in progress)&amp;RPage &amp;P of &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -34299,6 +34419,14 @@
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader>&amp;RDRAFT</oddHeader>
+    <oddFooter>&amp;LDRAFT - not issued (S0, work in progress)&amp;RPage &amp;P of &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -35680,6 +35808,14 @@
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader>&amp;RDRAFT</oddHeader>
+    <oddFooter>&amp;LDRAFT - not issued (S0, work in progress)&amp;RPage &amp;P of &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -37355,6 +37491,14 @@
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader>&amp;RDRAFT</oddHeader>
+    <oddFooter>&amp;LDRAFT - not issued (S0, work in progress)&amp;RPage &amp;P of &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -38740,6 +38884,14 @@
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader>&amp;RDRAFT</oddHeader>
+    <oddFooter>&amp;LDRAFT - not issued (S0, work in progress)&amp;RPage &amp;P of &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -40023,5 +40175,13 @@
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader>&amp;RDRAFT</oddHeader>
+    <oddFooter>&amp;LDRAFT - not issued (S0, work in progress)&amp;RPage &amp;P of &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
--- a/KUT_DOCS_WORKING/issued/KUT_Master_Information_Delivery_Plan.xlsx
+++ b/KUT_DOCS_WORKING/issued/KUT_Master_Information_Delivery_Plan.xlsx
@@ -1055,8 +1055,8 @@
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter>
-    <oddHeader>&amp;RDRAFT</oddHeader>
-    <oddFooter>&amp;LDRAFT - not issued (S0, work in progress)&amp;RPage &amp;P of &amp;N</oddFooter>
+    <oddHeader>&amp;L&amp;"Calibri,Bold"&amp;9KAMPALA UGANDA TEMPLE&amp;C&amp;"Calibri,Bold"&amp;9&amp;A&amp;R&amp;9KUT-SMB-ZZ-ZZ-SH-Z-0001   Rev P01</oddHeader>
+    <oddFooter>&amp;L&amp;9&amp;KC00000DRAFT - not issued (S0, work in progress)&amp;C&amp;8Symbion Consulting Group Studios - Information Manager&amp;R&amp;9&amp;A   Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -2174,8 +2174,8 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;RDRAFT</oddHeader>
-    <oddFooter>&amp;LDRAFT - not issued (S0, work in progress)&amp;RPage &amp;P of &amp;N</oddFooter>
+    <oddHeader>&amp;L&amp;"Calibri,Bold"&amp;9KAMPALA UGANDA TEMPLE&amp;C&amp;"Calibri,Bold"&amp;9&amp;A&amp;R&amp;9KUT-SMB-ZZ-ZZ-SH-Z-0001   Rev P01</oddHeader>
+    <oddFooter>&amp;L&amp;9&amp;KC00000DRAFT - not issued (S0, work in progress)&amp;C&amp;8Symbion Consulting Group Studios - Information Manager&amp;R&amp;9&amp;A   Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -3285,8 +3285,8 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;RDRAFT</oddHeader>
-    <oddFooter>&amp;LDRAFT - not issued (S0, work in progress)&amp;RPage &amp;P of &amp;N</oddFooter>
+    <oddHeader>&amp;L&amp;"Calibri,Bold"&amp;9KAMPALA UGANDA TEMPLE&amp;C&amp;"Calibri,Bold"&amp;9&amp;A&amp;R&amp;9KUT-SMB-ZZ-ZZ-SH-Z-0001   Rev P01</oddHeader>
+    <oddFooter>&amp;L&amp;9&amp;KC00000DRAFT - not issued (S0, work in progress)&amp;C&amp;8Symbion Consulting Group Studios - Information Manager&amp;R&amp;9&amp;A   Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -4588,8 +4588,8 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;RDRAFT</oddHeader>
-    <oddFooter>&amp;LDRAFT - not issued (S0, work in progress)&amp;RPage &amp;P of &amp;N</oddFooter>
+    <oddHeader>&amp;L&amp;"Calibri,Bold"&amp;9KAMPALA UGANDA TEMPLE&amp;C&amp;"Calibri,Bold"&amp;9&amp;A&amp;R&amp;9KUT-SMB-ZZ-ZZ-SH-Z-0001   Rev P01</oddHeader>
+    <oddFooter>&amp;L&amp;9&amp;KC00000DRAFT - not issued (S0, work in progress)&amp;C&amp;8Symbion Consulting Group Studios - Information Manager&amp;R&amp;9&amp;A   Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -5507,8 +5507,8 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;RDRAFT</oddHeader>
-    <oddFooter>&amp;LDRAFT - not issued (S0, work in progress)&amp;RPage &amp;P of &amp;N</oddFooter>
+    <oddHeader>&amp;L&amp;"Calibri,Bold"&amp;9KAMPALA UGANDA TEMPLE&amp;C&amp;"Calibri,Bold"&amp;9&amp;A&amp;R&amp;9KUT-SMB-ZZ-ZZ-SH-Z-0001   Rev P01</oddHeader>
+    <oddFooter>&amp;L&amp;9&amp;KC00000DRAFT - not issued (S0, work in progress)&amp;C&amp;8Symbion Consulting Group Studios - Information Manager&amp;R&amp;9&amp;A   Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -6626,8 +6626,8 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;RDRAFT</oddHeader>
-    <oddFooter>&amp;LDRAFT - not issued (S0, work in progress)&amp;RPage &amp;P of &amp;N</oddFooter>
+    <oddHeader>&amp;L&amp;"Calibri,Bold"&amp;9KAMPALA UGANDA TEMPLE&amp;C&amp;"Calibri,Bold"&amp;9&amp;A&amp;R&amp;9KUT-SMB-ZZ-ZZ-SH-Z-0001   Rev P01</oddHeader>
+    <oddFooter>&amp;L&amp;9&amp;KC00000DRAFT - not issued (S0, work in progress)&amp;C&amp;8Symbion Consulting Group Studios - Information Manager&amp;R&amp;9&amp;A   Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -7745,8 +7745,8 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;RDRAFT</oddHeader>
-    <oddFooter>&amp;LDRAFT - not issued (S0, work in progress)&amp;RPage &amp;P of &amp;N</oddFooter>
+    <oddHeader>&amp;L&amp;"Calibri,Bold"&amp;9KAMPALA UGANDA TEMPLE&amp;C&amp;"Calibri,Bold"&amp;9&amp;A&amp;R&amp;9KUT-SMB-ZZ-ZZ-SH-Z-0001   Rev P01</oddHeader>
+    <oddFooter>&amp;L&amp;9&amp;KC00000DRAFT - not issued (S0, work in progress)&amp;C&amp;8Symbion Consulting Group Studios - Information Manager&amp;R&amp;9&amp;A   Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -8762,8 +8762,8 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;RDRAFT</oddHeader>
-    <oddFooter>&amp;LDRAFT - not issued (S0, work in progress)&amp;RPage &amp;P of &amp;N</oddFooter>
+    <oddHeader>&amp;L&amp;"Calibri,Bold"&amp;9KAMPALA UGANDA TEMPLE&amp;C&amp;"Calibri,Bold"&amp;9&amp;A&amp;R&amp;9KUT-SMB-ZZ-ZZ-SH-Z-0001   Rev P01</oddHeader>
+    <oddFooter>&amp;L&amp;9&amp;KC00000DRAFT - not issued (S0, work in progress)&amp;C&amp;8Symbion Consulting Group Studios - Information Manager&amp;R&amp;9&amp;A   Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -10045,8 +10045,8 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;RDRAFT</oddHeader>
-    <oddFooter>&amp;LDRAFT - not issued (S0, work in progress)&amp;RPage &amp;P of &amp;N</oddFooter>
+    <oddHeader>&amp;L&amp;"Calibri,Bold"&amp;9KAMPALA UGANDA TEMPLE&amp;C&amp;"Calibri,Bold"&amp;9&amp;A&amp;R&amp;9KUT-SMB-ZZ-ZZ-SH-Z-0001   Rev P01</oddHeader>
+    <oddFooter>&amp;L&amp;9&amp;KC00000DRAFT - not issued (S0, work in progress)&amp;C&amp;8Symbion Consulting Group Studios - Information Manager&amp;R&amp;9&amp;A   Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -11248,8 +11248,8 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;RDRAFT</oddHeader>
-    <oddFooter>&amp;LDRAFT - not issued (S0, work in progress)&amp;RPage &amp;P of &amp;N</oddFooter>
+    <oddHeader>&amp;L&amp;"Calibri,Bold"&amp;9KAMPALA UGANDA TEMPLE&amp;C&amp;"Calibri,Bold"&amp;9&amp;A&amp;R&amp;9KUT-SMB-ZZ-ZZ-SH-Z-0001   Rev P01</oddHeader>
+    <oddFooter>&amp;L&amp;9&amp;KC00000DRAFT - not issued (S0, work in progress)&amp;C&amp;8Symbion Consulting Group Studios - Information Manager&amp;R&amp;9&amp;A   Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -13297,8 +13297,8 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;RDRAFT</oddHeader>
-    <oddFooter>&amp;LDRAFT - not issued (S0, work in progress)&amp;RPage &amp;P of &amp;N</oddFooter>
+    <oddHeader>&amp;L&amp;"Calibri,Bold"&amp;9KAMPALA UGANDA TEMPLE&amp;C&amp;"Calibri,Bold"&amp;9&amp;A&amp;R&amp;9KUT-SMB-ZZ-ZZ-SH-Z-0001   Rev P01</oddHeader>
+    <oddFooter>&amp;L&amp;9&amp;KC00000DRAFT - not issued (S0, work in progress)&amp;C&amp;8Symbion Consulting Group Studios - Information Manager&amp;R&amp;9&amp;A   Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -13650,8 +13650,8 @@
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter>
-    <oddHeader>&amp;RDRAFT</oddHeader>
-    <oddFooter>&amp;LDRAFT - not issued (S0, work in progress)&amp;RPage &amp;P of &amp;N</oddFooter>
+    <oddHeader>&amp;L&amp;"Calibri,Bold"&amp;9KAMPALA UGANDA TEMPLE&amp;C&amp;"Calibri,Bold"&amp;9&amp;A&amp;R&amp;9KUT-SMB-ZZ-ZZ-SH-Z-0001   Rev P01</oddHeader>
+    <oddFooter>&amp;L&amp;9&amp;KC00000DRAFT - not issued (S0, work in progress)&amp;C&amp;8Symbion Consulting Group Studios - Information Manager&amp;R&amp;9&amp;A   Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -14408,8 +14408,8 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter>
-    <oddHeader>&amp;RDRAFT</oddHeader>
-    <oddFooter>&amp;LDRAFT - not issued (S0, work in progress)&amp;RPage &amp;P of &amp;N</oddFooter>
+    <oddHeader>&amp;L&amp;"Calibri,Bold"&amp;9KAMPALA UGANDA TEMPLE&amp;C&amp;"Calibri,Bold"&amp;9&amp;A&amp;R&amp;9KUT-SMB-ZZ-ZZ-SH-Z-0001   Rev P01</oddHeader>
+    <oddFooter>&amp;L&amp;9&amp;KC00000DRAFT - not issued (S0, work in progress)&amp;C&amp;8Symbion Consulting Group Studios - Information Manager&amp;R&amp;9&amp;A   Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -27097,8 +27097,8 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;RDRAFT</oddHeader>
-    <oddFooter>&amp;LDRAFT - not issued (S0, work in progress)&amp;RPage &amp;P of &amp;N</oddFooter>
+    <oddHeader>&amp;L&amp;"Calibri,Bold"&amp;9KAMPALA UGANDA TEMPLE&amp;C&amp;"Calibri,Bold"&amp;9&amp;A&amp;R&amp;9KUT-SMB-ZZ-ZZ-SH-Z-0001   Rev P01</oddHeader>
+    <oddFooter>&amp;L&amp;9&amp;KC00000DRAFT - not issued (S0, work in progress)&amp;C&amp;8Symbion Consulting Group Studios - Information Manager&amp;R&amp;9&amp;A   Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -32884,8 +32884,8 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;RDRAFT</oddHeader>
-    <oddFooter>&amp;LDRAFT - not issued (S0, work in progress)&amp;RPage &amp;P of &amp;N</oddFooter>
+    <oddHeader>&amp;L&amp;"Calibri,Bold"&amp;9KAMPALA UGANDA TEMPLE&amp;C&amp;"Calibri,Bold"&amp;9&amp;A&amp;R&amp;9KUT-SMB-ZZ-ZZ-SH-Z-0001   Rev P01</oddHeader>
+    <oddFooter>&amp;L&amp;9&amp;KC00000DRAFT - not issued (S0, work in progress)&amp;C&amp;8Symbion Consulting Group Studios - Information Manager&amp;R&amp;9&amp;A   Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -34767,8 +34767,8 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;RDRAFT</oddHeader>
-    <oddFooter>&amp;LDRAFT - not issued (S0, work in progress)&amp;RPage &amp;P of &amp;N</oddFooter>
+    <oddHeader>&amp;L&amp;"Calibri,Bold"&amp;9KAMPALA UGANDA TEMPLE&amp;C&amp;"Calibri,Bold"&amp;9&amp;A&amp;R&amp;9KUT-SMB-ZZ-ZZ-SH-Z-0001   Rev P01</oddHeader>
+    <oddFooter>&amp;L&amp;9&amp;KC00000DRAFT - not issued (S0, work in progress)&amp;C&amp;8Symbion Consulting Group Studios - Information Manager&amp;R&amp;9&amp;A   Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -36168,8 +36168,8 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;RDRAFT</oddHeader>
-    <oddFooter>&amp;LDRAFT - not issued (S0, work in progress)&amp;RPage &amp;P of &amp;N</oddFooter>
+    <oddHeader>&amp;L&amp;"Calibri,Bold"&amp;9KAMPALA UGANDA TEMPLE&amp;C&amp;"Calibri,Bold"&amp;9&amp;A&amp;R&amp;9KUT-SMB-ZZ-ZZ-SH-Z-0001   Rev P01</oddHeader>
+    <oddFooter>&amp;L&amp;9&amp;KC00000DRAFT - not issued (S0, work in progress)&amp;C&amp;8Symbion Consulting Group Studios - Information Manager&amp;R&amp;9&amp;A   Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -37863,8 +37863,8 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;RDRAFT</oddHeader>
-    <oddFooter>&amp;LDRAFT - not issued (S0, work in progress)&amp;RPage &amp;P of &amp;N</oddFooter>
+    <oddHeader>&amp;L&amp;"Calibri,Bold"&amp;9KAMPALA UGANDA TEMPLE&amp;C&amp;"Calibri,Bold"&amp;9&amp;A&amp;R&amp;9KUT-SMB-ZZ-ZZ-SH-Z-0001   Rev P01</oddHeader>
+    <oddFooter>&amp;L&amp;9&amp;KC00000DRAFT - not issued (S0, work in progress)&amp;C&amp;8Symbion Consulting Group Studios - Information Manager&amp;R&amp;9&amp;A   Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -39268,8 +39268,8 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;RDRAFT</oddHeader>
-    <oddFooter>&amp;LDRAFT - not issued (S0, work in progress)&amp;RPage &amp;P of &amp;N</oddFooter>
+    <oddHeader>&amp;L&amp;"Calibri,Bold"&amp;9KAMPALA UGANDA TEMPLE&amp;C&amp;"Calibri,Bold"&amp;9&amp;A&amp;R&amp;9KUT-SMB-ZZ-ZZ-SH-Z-0001   Rev P01</oddHeader>
+    <oddFooter>&amp;L&amp;9&amp;KC00000DRAFT - not issued (S0, work in progress)&amp;C&amp;8Symbion Consulting Group Studios - Information Manager&amp;R&amp;9&amp;A   Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -40571,8 +40571,8 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;RDRAFT</oddHeader>
-    <oddFooter>&amp;LDRAFT - not issued (S0, work in progress)&amp;RPage &amp;P of &amp;N</oddFooter>
+    <oddHeader>&amp;L&amp;"Calibri,Bold"&amp;9KAMPALA UGANDA TEMPLE&amp;C&amp;"Calibri,Bold"&amp;9&amp;A&amp;R&amp;9KUT-SMB-ZZ-ZZ-SH-Z-0001   Rev P01</oddHeader>
+    <oddFooter>&amp;L&amp;9&amp;KC00000DRAFT - not issued (S0, work in progress)&amp;C&amp;8Symbion Consulting Group Studios - Information Manager&amp;R&amp;9&amp;A   Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
